--- a/Ahmedabad-February-2026.xlsx
+++ b/Ahmedabad-February-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="65">
   <si>
     <t>Sr. No</t>
   </si>
@@ -94,6 +94,9 @@
     <t>Profit %</t>
   </si>
   <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
     <t>Ahmedabad</t>
   </si>
   <si>
@@ -169,25 +172,22 @@
     <t>AMAZE</t>
   </si>
   <si>
-    <t>Crysta</t>
-  </si>
-  <si>
-    <t>CITROEN EV3</t>
+    <t>CRYSTA</t>
+  </si>
+  <si>
+    <t>CITROEN</t>
   </si>
   <si>
     <t>HYCROSS</t>
   </si>
   <si>
-    <t>INVICTO ZETA</t>
+    <t>INVICTO</t>
   </si>
   <si>
     <t>15/05/2025</t>
   </si>
   <si>
     <t>21/08/2025</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
   <si>
     <t>29/03/2022</t>
@@ -570,10 +570,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z23"/>
+  <dimension ref="A1:AA23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -652,28 +652,31 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:27">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2">
         <v>2026</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H2">
         <v>51290</v>
@@ -733,27 +736,27 @@
         <v>15.21</v>
       </c>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:27">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>2026</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H3">
         <v>50336</v>
@@ -813,27 +816,27 @@
         <v>11.14</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:27">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4">
         <v>2026</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H4">
         <v>28117</v>
@@ -893,27 +896,27 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:27">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5">
         <v>2026</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H5">
         <v>24592</v>
@@ -973,24 +976,24 @@
         <v>8.56</v>
       </c>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:27">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6">
         <v>2026</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G6" s="2">
         <v>44410</v>
@@ -1053,24 +1056,24 @@
         <v>46.85</v>
       </c>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:27">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7">
         <v>2026</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G7" s="2">
         <v>44990</v>
@@ -1133,24 +1136,24 @@
         <v>11.39</v>
       </c>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" spans="1:27">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8">
         <v>2026</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G8" s="2">
         <v>45055</v>
@@ -1213,27 +1216,27 @@
         <v>-3.09</v>
       </c>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9" spans="1:27">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9">
         <v>2026</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>51</v>
-      </c>
-      <c r="G9" t="s">
-        <v>57</v>
+        <v>52</v>
+      </c>
+      <c r="G9" s="2">
+        <v>44350</v>
       </c>
       <c r="H9">
         <v>99985</v>
@@ -1293,27 +1296,27 @@
         <v>39.53</v>
       </c>
     </row>
-    <row r="10" spans="1:26">
+    <row r="10" spans="1:27">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10">
         <v>2026</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
-        <v>51</v>
-      </c>
-      <c r="G10" t="s">
-        <v>57</v>
+        <v>52</v>
+      </c>
+      <c r="G10" s="2">
+        <v>44652</v>
       </c>
       <c r="H10">
         <v>47795</v>
@@ -1373,24 +1376,24 @@
         <v>49.08</v>
       </c>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:27">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11">
         <v>2026</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G11" s="2">
         <v>44077</v>
@@ -1453,24 +1456,24 @@
         <v>51.77</v>
       </c>
     </row>
-    <row r="12" spans="1:26">
+    <row r="12" spans="1:27">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <v>2026</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G12" s="2">
         <v>44206</v>
@@ -1533,24 +1536,24 @@
         <v>42.31</v>
       </c>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" spans="1:27">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D13">
         <v>2026</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G13" t="s">
         <v>58</v>
@@ -1613,24 +1616,24 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:27">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D14">
         <v>2026</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G14" s="2">
         <v>44746</v>
@@ -1693,24 +1696,24 @@
         <v>37.15</v>
       </c>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:27">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D15">
         <v>2026</v>
       </c>
       <c r="E15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G15" t="s">
         <v>59</v>
@@ -1773,24 +1776,24 @@
         <v>48.29</v>
       </c>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" spans="1:27">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D16">
         <v>2026</v>
       </c>
       <c r="E16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G16" t="s">
         <v>60</v>
@@ -1858,19 +1861,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17">
         <v>2026</v>
       </c>
       <c r="E17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G17" t="s">
         <v>61</v>
@@ -1938,19 +1941,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D18">
         <v>2026</v>
       </c>
       <c r="E18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G18" t="s">
         <v>61</v>
@@ -2018,19 +2021,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19">
         <v>2026</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F19" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G19" t="s">
         <v>62</v>
@@ -2098,19 +2101,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D20">
         <v>2026</v>
       </c>
       <c r="E20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G20" t="s">
         <v>63</v>
@@ -2178,19 +2181,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D21">
         <v>2026</v>
       </c>
       <c r="E21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G21" t="s">
         <v>63</v>
@@ -2258,19 +2261,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D22">
         <v>2026</v>
       </c>
       <c r="E22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G22" s="2">
         <v>44960</v>
@@ -2338,19 +2341,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D23">
         <v>2026</v>
       </c>
       <c r="E23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G23" t="s">
         <v>64</v>
